--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -583,7 +583,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧です。「取扱い」が「お諮りする内容を含む」の資料には、受託者の判断・推奨・試算・留保が含まれます。確定値ではありません。</t>
+          <t>今回送付する資料の一覧です。「取扱い」が「お諮りする内容を含む」の資料には、受託者の判断・推奨・試算が含まれます。確定値ではありません。「送付可能（留保明記済み）」の資料にも、重複の取扱いが未確定の数値等が含まれる場合があり、その旨は各資料の本文に明記しています。</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,8 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -774,7 +775,8 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -906,7 +908,8 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -931,7 +934,8 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -956,7 +960,8 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -981,7 +986,8 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1012,8 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1038,8 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1303,8 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1329,8 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1355,8 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1381,8 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1407,8 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1465,8 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1491,8 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1517,8 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1600,8 @@
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1626,8 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1652,8 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1670,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料（更新版）_校正反映.docx</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -1666,7 +1685,8 @@
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1696,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_校正反映.odt</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -1691,7 +1711,8 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1737,8 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>そのまま</t>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1778,7 @@
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>うち そのまま 22件／お諮りする内容を含む 21件</t>
+          <t>うち 送付可能（留保明記済み）22件／お諮りする内容を含む 21件</t>
         </is>
       </c>
       <c r="D57" s="11" t="n"/>
@@ -1767,7 +1789,7 @@
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
-注3）本一覧のほか、図表のPNG（34点）を同送しています。
+注3）本一覧のほか、計画本文に掲載する図表の画像（PNG）を送付用ZIPの「03_図表の画像」に収めています。
 注4）本業務で作成した資料のうち、受託者の作業過程の記録（校正の記録、自己点検の記録、修正指示書、進行者の手元資料）は本一覧に含めていません。業務仕様書４（10）「その他業務で作成した資料　一式」として保管しており、納品時又はお求めに応じて提出します。</t>
         </is>
       </c>
@@ -1858,7 +1880,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>認定者数・サービス見込量・給付費・保険料のすべてが確定しません。第6章の算定が着手できません。</t>
+          <t>第6章の採用値、及び第3段階（給付費・保険料）を確定できません。第1段階（人口・認定者数）と第2段階（サービス見込量）の試算は本送付に含めています。</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -745,7 +745,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>80段落 11表</t>
+          <t>90段落 12表</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -2140,7 +2140,7 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>注）資料の全体は「必要事項の一覧」（不足資料18件・確認事項56件）及び「確認依頼書」に掲げています。</t>
+          <t>注）資料の全体は「必要事項の一覧」（不足資料16件・確認事項56件）及び「確認依頼書」に掲げています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>90段落 12表</t>
+          <t>92段落 13表</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -1392,55 +1392,55 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>4シート</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>送付可能
 （留保明記済み）</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>【6　ご確認・ご決定をお願いする資料】</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="34" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1450,23 +1450,22 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1475,17 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -1502,17 +1501,17 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -1528,22 +1527,23 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1553,55 +1553,54 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>9シート</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>【7　工程】</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="34" customHeight="1">
-      <c r="A48" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>187段落 8表</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1611,17 +1610,17 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>187段落 8表</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -1637,17 +1636,17 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -1657,36 +1656,36 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>【8　会議】</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="34" customHeight="1">
-      <c r="A52" s="5" t="n">
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>117段落 14表</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_送付資料一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>送付可能
 （留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>【8　会議】</t>
         </is>
       </c>
     </row>
@@ -1696,17 +1695,17 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>ODF形式</t>
+          <t>117段落 14表</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -1722,17 +1721,17 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>ODF形式</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -1748,44 +1747,70 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>会議で用いるヒアリングシート</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>38段落 21表</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="34" customHeight="1">
+      <c r="A56" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_3町ヒアリング資料.docx</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>3町へのヒアリング資料。設問はご確認を要する</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>135段落 11表</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="9" t="inlineStr">
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B57" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="C57" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）22件／お諮りする内容を含む 21件</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="n"/>
-      <c r="E57" s="12" t="n"/>
-    </row>
-    <row r="59" ht="140" customHeight="1">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="B58" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）22件／お諮りする内容を含む 22件</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="12" t="n"/>
+    </row>
+    <row r="60" ht="140" customHeight="1">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -1796,15 +1821,15 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C58:E58"/>
     <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A48:E48"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A41:E41"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A17:E17"/>
   </mergeCells>
@@ -2140,7 +2165,7 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>注）資料の全体は「必要事項の一覧」（不足資料16件・確認事項56件）及び「確認依頼書」に掲げています。</t>
+          <t>注）資料の全体は「必要事項の一覧」（不足資料17件・確認事項56件）及び「確認依頼書」に掲げています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>国勢調査・住民基本台帳との突合</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -1437,35 +1437,36 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>国勢調査・住民基本台帳との突合</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>【6　ご確認・ご決定をお願いする資料】</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1475,23 +1476,22 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1501,17 +1501,17 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -1527,17 +1527,17 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -1553,22 +1553,23 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1578,55 +1579,54 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>9シート</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>【7　工程】</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>187段落 8表</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1636,17 +1636,17 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>187段落 8表</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -1662,17 +1662,17 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -1682,36 +1682,36 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>【8　会議】</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="34" customHeight="1">
-      <c r="A53" s="5" t="n">
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>117段落 14表</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_送付資料一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>送付可能
 （留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>【8　会議】</t>
         </is>
       </c>
     </row>
@@ -1721,17 +1721,17 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>ODF形式</t>
+          <t>117段落 14表</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -1747,17 +1747,17 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>ODF形式</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -1773,44 +1773,70 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>会議で用いるヒアリングシート</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>38段落 21表</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="34" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_3町ヒアリング資料.docx</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>3町へのヒアリング資料。設問はご確認を要する</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>135段落 11表</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="9" t="inlineStr">
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B58" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）22件／お諮りする内容を含む 22件</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="n"/>
-      <c r="E58" s="12" t="n"/>
-    </row>
-    <row r="60" ht="140" customHeight="1">
-      <c r="A60" s="13" t="inlineStr">
+      <c r="B59" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）23件／お諮りする内容を含む 22件</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="12" t="n"/>
+    </row>
+    <row r="61" ht="140" customHeight="1">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -1821,16 +1847,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A61:E61"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A49:E49"/>
     <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C59:E59"/>
     <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -1430,10 +1430,9 @@
           <t>4シート</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1443,17 +1442,17 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>国勢調査・住民基本台帳との突合</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -1463,35 +1462,36 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>国勢調査・住民基本台帳との突合</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>【6　ご確認・ご決定をお願いする資料】</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1501,23 +1501,22 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1527,17 +1526,17 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -1553,17 +1552,17 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -1579,22 +1578,23 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1604,55 +1604,54 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>9シート</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>【7　工程】</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="34" customHeight="1">
-      <c r="A50" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>187段落 8表</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1662,17 +1661,17 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>187段落 8表</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -1688,17 +1687,17 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
@@ -1708,36 +1707,36 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>【8　会議】</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="34" customHeight="1">
-      <c r="A54" s="5" t="n">
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>117段落 14表</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_送付資料一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>送付可能
 （留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>【8　会議】</t>
         </is>
       </c>
     </row>
@@ -1747,17 +1746,17 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>ODF形式</t>
+          <t>117段落 14表</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -1773,17 +1772,17 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>ODF形式</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -1799,44 +1798,70 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>会議で用いるヒアリングシート</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>38段落 21表</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="34" customHeight="1">
+      <c r="A58" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_3町ヒアリング資料.docx</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>3町へのヒアリング資料。設問はご確認を要する</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>135段落 11表</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="9" t="inlineStr">
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B59" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="C59" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）23件／お諮りする内容を含む 22件</t>
-        </is>
-      </c>
-      <c r="D59" s="11" t="n"/>
-      <c r="E59" s="12" t="n"/>
-    </row>
-    <row r="61" ht="140" customHeight="1">
-      <c r="A61" s="13" t="inlineStr">
+      <c r="B60" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）23件／お諮りする内容を含む 23件</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="12" t="n"/>
+    </row>
+    <row r="62" ht="140" customHeight="1">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -1847,16 +1872,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="C60:E60"/>
     <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A54:E54"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A49:E49"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="C59:E59"/>
     <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -1427,7 +1427,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -2216,7 +2216,7 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>注）資料の全体は「必要事項の一覧」（不足資料17件・確認事項56件）及び「確認依頼書」に掲げています。</t>
+          <t>注）資料の全体は「必要事項の一覧」（不足資料18件・確認事項56件）及び「確認依頼書」に掲げています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -1588,7 +1588,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>国勢調査・住民基本台帳との突合</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -1488,55 +1488,75 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>【6　ご確認・ご決定をお願いする資料】</t>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="34" customHeight="1">
       <c r="A44" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
     <row r="45" ht="34" customHeight="1">
       <c r="A45" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>5シート</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -1548,47 +1568,46 @@
     </row>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
     <row r="47" ht="34" customHeight="1">
       <c r="A47" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -1598,28 +1617,10 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="34" customHeight="1">
-      <c r="A48" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>【6　ご確認・ご決定をお願いする資料】</t>
         </is>
       </c>
     </row>
@@ -1629,17 +1630,17 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>3シート</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
@@ -1648,30 +1649,49 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>【7　工程】</t>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>不足資料・確認事項の一覧</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>8シート</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
     <row r="51" ht="34" customHeight="1">
       <c r="A51" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>187段落 8表</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -1683,21 +1703,21 @@
     </row>
     <row r="52" ht="34" customHeight="1">
       <c r="A52" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
@@ -1709,80 +1729,78 @@
     </row>
     <row r="53" ht="34" customHeight="1">
       <c r="A53" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>【8　会議】</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="34" customHeight="1">
-      <c r="A55" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>117段落 14表</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="A54" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_概要版の構成案.xlsx</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>【7　工程】</t>
         </is>
       </c>
     </row>
     <row r="56" ht="34" customHeight="1">
       <c r="A56" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>ODF形式</t>
+          <t>187段落 8表</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -1794,21 +1812,21 @@
     </row>
     <row r="57" ht="34" customHeight="1">
       <c r="A57" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -1820,48 +1838,185 @@
     </row>
     <row r="58" ht="34" customHeight="1">
       <c r="A58" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_送付資料一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>【8　会議】</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>キックオフ会議の配布資料（最新版）</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>117段落 14表</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="34" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>議事録（校正反映後）</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>ODF形式</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="34" customHeight="1">
+      <c r="A62" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>ODF形式</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>会議で用いるヒアリングシート</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>38段落 21表</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="34" customHeight="1">
+      <c r="A64" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_3町ヒアリング資料.docx</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>3町へのヒアリング資料。設問はご確認を要する</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>135段落 11表</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B60" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）23件／お諮りする内容を含む 23件</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="n"/>
-      <c r="E60" s="12" t="n"/>
-    </row>
-    <row r="62" ht="140" customHeight="1">
-      <c r="A62" s="13" t="inlineStr">
+      <c r="B66" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）28件／お諮りする内容を含む 24件</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="12" t="n"/>
+    </row>
+    <row r="68" ht="140" customHeight="1">
+      <c r="A68" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -1872,15 +2027,15 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="C60:E60"/>
     <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="C66:E66"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A54:E54"/>
     <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A68:E68"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A17:E17"/>
   </mergeCells>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>669段落 114表</t>
+          <t>716段落 122表</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>92段落 13表</t>
+          <t>103段落 15表</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>716段落 122表</t>
+          <t>717段落 122表</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -1131,17 +1131,17 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -1156,17 +1156,17 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -1206,17 +1206,17 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -1231,17 +1231,17 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -1256,55 +1256,54 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>10シート</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>【5　基礎データの点検と突合】</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>見える化B系列の受領点検</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>7シート</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1313,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>見える化D系列の受領点検</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -1340,17 +1339,17 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>見える化D系列の受領点検</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -1366,17 +1365,17 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>3町提供の社会資源一覧との突合。担当者名・連絡先は収録していない</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -1392,22 +1391,23 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>3町提供の社会資源一覧との突合。担当者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -1442,23 +1442,22 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1468,17 +1467,17 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -1494,17 +1493,17 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -1520,12 +1519,12 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -1546,12 +1545,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -1572,22 +1571,23 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1597,55 +1597,55 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_基金条例の確認.xlsx</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>【6　ご確認・ご決定をお願いする資料】</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1655,23 +1655,22 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1681,17 +1680,17 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -1707,17 +1706,17 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
@@ -1733,22 +1732,23 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1758,55 +1758,54 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="34" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>9シート</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>【7　工程】</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="34" customHeight="1">
-      <c r="A56" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>187段落 8表</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1816,17 +1815,17 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>187段落 8表</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -1842,56 +1841,56 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_業務工程管理表.xlsx</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="34" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>3シート</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>【8　会議】</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="34" customHeight="1">
-      <c r="A60" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>117段落 14表</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1901,17 +1900,17 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>ODF形式</t>
+          <t>117段落 14表</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -1927,12 +1926,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -1953,17 +1952,17 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>ODF形式</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -1979,44 +1978,70 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>会議で用いるヒアリングシート</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>38段落 21表</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="34" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_3町ヒアリング資料.docx</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>3町へのヒアリング資料。設問はご確認を要する</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>135段落 11表</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="9" t="inlineStr">
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B66" s="9" t="n">
-        <v>52</v>
-      </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）28件／お諮りする内容を含む 24件</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="n"/>
-      <c r="E66" s="12" t="n"/>
-    </row>
-    <row r="68" ht="140" customHeight="1">
-      <c r="A68" s="13" t="inlineStr">
+      <c r="B67" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）28件／お諮りする内容を含む 25件</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="n"/>
+      <c r="E67" s="12" t="n"/>
+    </row>
+    <row r="69" ht="140" customHeight="1">
+      <c r="A69" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2027,17 +2052,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A49:E49"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A56:E56"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>717段落 122表</t>
+          <t>738段落 124表</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>33シート</t>
+          <t>36シート</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>103段落 15表</t>
+          <t>112段落 16表</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -841,12 +841,12 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -2023,25 +2023,50 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="9" t="inlineStr">
+    <row r="66" ht="34" customHeight="1">
+      <c r="A66" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_3町別の論点整理.xlsx</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点12件、3町共通の論点8件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B67" s="9" t="n">
-        <v>53</v>
-      </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）28件／お諮りする内容を含む 25件</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="n"/>
-      <c r="E67" s="12" t="n"/>
-    </row>
-    <row r="69" ht="140" customHeight="1">
-      <c r="A69" s="13" t="inlineStr">
+      <c r="B68" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）28件／お諮りする内容を含む 26件</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="n"/>
+      <c r="E68" s="12" t="n"/>
+    </row>
+    <row r="70" ht="140" customHeight="1">
+      <c r="A70" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2052,8 +2077,6 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="A69:E69"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
@@ -2061,6 +2084,8 @@
     <mergeCell ref="A60:E60"/>
     <mergeCell ref="A49:E49"/>
     <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="A70:E70"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A56:E56"/>
   </mergeCells>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1181,22 +1181,23 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1207,17 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -1231,17 +1232,17 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -1256,17 +1257,17 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1281,55 +1282,54 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>10シート</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>【5　基礎データの点検と突合】</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="34" customHeight="1">
-      <c r="A36" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>見える化B系列の受領点検</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>7シート</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>見える化D系列の受領点検</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -1365,17 +1365,17 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>見える化D系列の受領点検</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>3町提供の社会資源一覧との突合。担当者名・連絡先は収録していない</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -1417,22 +1417,23 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>3町提供の社会資源一覧との突合。担当者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1442,17 +1443,17 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -1467,23 +1468,22 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1493,17 +1493,17 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -1519,17 +1519,17 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -1597,22 +1597,23 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1622,55 +1623,55 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_基金条例の確認.xlsx</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>【6　ご確認・ご決定をお願いする資料】</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="34" customHeight="1">
-      <c r="A50" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1680,23 +1681,22 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1706,17 +1706,17 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -1758,22 +1758,23 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1783,55 +1784,54 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="34" customHeight="1">
+      <c r="A56" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>9シート</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>【7　工程】</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="34" customHeight="1">
-      <c r="A57" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>187段落 8表</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1841,17 +1841,17 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>187段落 8表</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
@@ -1867,56 +1867,56 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_業務工程管理表.xlsx</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>3シート</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>【8　会議】</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="34" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>117段落 14表</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1926,17 +1926,17 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>ODF形式</t>
+          <t>117段落 14表</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -1978,17 +1978,17 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>ODF形式</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -2004,22 +2004,23 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町ヒアリング資料.docx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>3町へのヒアリング資料。設問はご確認を要する</t>
+          <t>会議で用いるヒアリングシート</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>135段落 11表</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>38段落 21表</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -2029,44 +2030,69 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_3町ヒアリング資料.docx</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>3町へのヒアリング資料。設問はご確認を要する</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>135段落 11表</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="34" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_3町別の論点整理.xlsx</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点12件、3町共通の論点8件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="9" t="inlineStr">
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B68" s="9" t="n">
-        <v>54</v>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）28件／お諮りする内容を含む 26件</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="n"/>
-      <c r="E68" s="12" t="n"/>
-    </row>
-    <row r="70" ht="140" customHeight="1">
-      <c r="A70" s="13" t="inlineStr">
+      <c r="B69" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）29件／お諮りする内容を含む 26件</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="n"/>
+      <c r="E69" s="12" t="n"/>
+    </row>
+    <row r="71" ht="140" customHeight="1">
+      <c r="A71" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2077,17 +2103,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="A71:E71"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A61:E61"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A56:E56"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>738段落 124表</t>
+          <t>739段落 124表</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -1181,23 +1181,22 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,684円・案B 6,593円・案C 6,789円、通し再計算による案C 6,755円）、確定を要する事項8件。採用案のご確認を要する</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1206,23 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1282,17 +1282,17 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -1307,55 +1307,54 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>10シート</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>【5　基礎データの点検と突合】</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="34" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>見える化B系列の受領点検</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>7シート</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1364,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>見える化D系列の受領点検</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -1391,17 +1390,17 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>見える化D系列の受領点検</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -1417,17 +1416,17 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>3町提供の社会資源一覧との突合。担当者名・連絡先は収録していない</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -1443,22 +1442,23 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>3町提供の社会資源一覧との突合。担当者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1468,17 +1468,17 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -1493,23 +1493,22 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1519,17 +1518,17 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -1545,17 +1544,17 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -1571,12 +1570,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -1597,12 +1596,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -1623,22 +1622,23 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1648,55 +1648,55 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_基金条例の確認.xlsx</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>【6　ご確認・ご決定をお願いする資料】</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="34" customHeight="1">
-      <c r="A51" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1706,23 +1706,22 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1732,17 +1731,17 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -1758,17 +1757,17 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -1784,22 +1783,23 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1809,55 +1809,54 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="34" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>9シート</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>【7　工程】</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="34" customHeight="1">
-      <c r="A58" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>187段落 8表</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1867,17 +1866,17 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>187段落 8表</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -1893,56 +1892,56 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_業務工程管理表.xlsx</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="34" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>3シート</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>【8　会議】</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="34" customHeight="1">
-      <c r="A62" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>117段落 14表</t>
-        </is>
-      </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1952,17 +1951,17 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>ODF形式</t>
+          <t>117段落 14表</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -1978,12 +1977,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -2004,17 +2003,17 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>ODF形式</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -2030,22 +2029,23 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町ヒアリング資料.docx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>3町へのヒアリング資料。設問はご確認を要する</t>
+          <t>会議で用いるヒアリングシート</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>135段落 11表</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>38段落 21表</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -2055,44 +2055,69 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_3町ヒアリング資料.docx</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>3町へのヒアリング資料。設問はご確認を要する</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>138段落 11表</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="34" customHeight="1">
+      <c r="A68" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_3町別の論点整理.xlsx</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点12件、3町共通の論点8件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="9" t="inlineStr">
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B69" s="9" t="n">
-        <v>55</v>
-      </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）29件／お諮りする内容を含む 26件</t>
-        </is>
-      </c>
-      <c r="D69" s="11" t="n"/>
-      <c r="E69" s="12" t="n"/>
-    </row>
-    <row r="71" ht="140" customHeight="1">
-      <c r="A71" s="13" t="inlineStr">
+      <c r="B70" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）29件／お諮りする内容を含む 27件</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="n"/>
+      <c r="E70" s="12" t="n"/>
+    </row>
+    <row r="72" ht="140" customHeight="1">
+      <c r="A72" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2103,16 +2128,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A62:E62"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A72:E72"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="C70:E70"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A58:E58"/>
     <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1206,23 +1206,22 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>8シート</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1231,23 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1282,17 +1282,17 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -1332,55 +1332,54 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>10シート</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>【5　基礎データの点検と突合】</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="34" customHeight="1">
-      <c r="A38" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>見える化B系列の受領点検</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>7シート</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1389,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>見える化D系列の受領点検</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -1416,17 +1415,17 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>見える化D系列の受領点検</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -1442,17 +1441,17 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>3町提供の社会資源一覧との突合。担当者名・連絡先は収録していない</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -1468,22 +1467,23 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>3町提供の社会資源一覧との突合。担当者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1493,17 +1493,17 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -1518,23 +1518,22 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1544,17 +1543,17 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -1570,17 +1569,17 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -1596,12 +1595,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -1622,12 +1621,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -1648,22 +1647,23 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1673,55 +1673,55 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_基金条例の確認.xlsx</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>送付可能
 （留保明記済み）</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>【6　ご確認・ご決定をお願いする資料】</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="34" customHeight="1">
-      <c r="A52" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1731,23 +1731,22 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1757,17 +1756,17 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -1783,17 +1782,17 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -1809,22 +1808,23 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1834,55 +1834,54 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="34" customHeight="1">
+      <c r="A58" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>9シート</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>【7　工程】</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="34" customHeight="1">
-      <c r="A59" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>187段落 8表</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1892,17 +1891,17 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>187段落 8表</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
@@ -1918,17 +1917,17 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -1938,36 +1937,36 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>【8　会議】</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="34" customHeight="1">
-      <c r="A63" s="5" t="n">
+    <row r="62" ht="34" customHeight="1">
+      <c r="A62" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>117段落 14表</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_送付資料一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>送付可能
 （留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>【8　会議】</t>
         </is>
       </c>
     </row>
@@ -1977,17 +1976,17 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>ODF形式</t>
+          <t>117段落 14表</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -2003,12 +2002,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -2029,17 +2028,17 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>ODF形式</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
@@ -2055,22 +2054,23 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町ヒアリング資料.docx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>3町へのヒアリング資料。設問はご確認を要する</t>
+          <t>会議で用いるヒアリングシート</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>138段落 11表</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>38段落 21表</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -2080,44 +2080,94 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_3町ヒアリング資料.docx</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>3町へのヒアリング資料。設問はご確認を要する</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>138段落 11表</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="34" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_3町別の論点整理.xlsx</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点12件、3町共通の論点8件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="9" t="inlineStr">
+    <row r="70" ht="34" customHeight="1">
+      <c r="A70" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>79段落 27表</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B70" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）29件／お諮りする内容を含む 27件</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="n"/>
-      <c r="E70" s="12" t="n"/>
-    </row>
-    <row r="72" ht="140" customHeight="1">
-      <c r="A72" s="13" t="inlineStr">
+      <c r="B72" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）29件／お諮りする内容を含む 29件</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="n"/>
+      <c r="E72" s="12" t="n"/>
+    </row>
+    <row r="74" ht="140" customHeight="1">
+      <c r="A74" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2128,16 +2178,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="A59:E59"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="A63:E63"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A74:E74"/>
     <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>739段落 124表</t>
+          <t>740段落 124表</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>3町提供の社会資源一覧との突合。担当者名・連絡先は収録していない</t>
+          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>79段落 27表</t>
+          <t>80段落 27表</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>740段落 124表</t>
+          <t>741段落 124表</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,684円・案B 6,593円・案C 6,789円、通し再計算による案C 6,755円）、確定を要する事項8件。採用案のご確認を要する</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1231,23 +1231,22 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>8シート</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1257,22 +1256,23 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1282,17 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -1332,17 +1332,17 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -1357,55 +1357,54 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>10シート</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>【5　基礎データの点検と突合】</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="34" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>見える化B系列の受領点検</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>7シート</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1414,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>見える化D系列の受領点検</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -1441,17 +1440,17 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>見える化D系列の受領点検</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -1467,17 +1466,17 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -1493,22 +1492,23 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -1543,23 +1543,22 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1569,17 +1568,17 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -1595,17 +1594,17 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -1621,12 +1620,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -1647,12 +1646,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -1673,22 +1672,23 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1698,55 +1698,55 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_基金条例の確認.xlsx</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>送付可能
 （留保明記済み）</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>【6　ご確認・ご決定をお願いする資料】</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="34" customHeight="1">
-      <c r="A53" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1756,23 +1756,22 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1782,17 +1781,17 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -1808,17 +1807,17 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -1834,22 +1833,23 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1859,55 +1859,54 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="34" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>9シート</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>【7　工程】</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="34" customHeight="1">
-      <c r="A60" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>187段落 8表</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1917,17 +1916,17 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>187段落 8表</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -1943,17 +1942,17 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
@@ -1963,36 +1962,36 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>【8　会議】</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="34" customHeight="1">
-      <c r="A64" s="5" t="n">
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>117段落 14表</t>
-        </is>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_送付資料一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>送付可能
 （留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>【8　会議】</t>
         </is>
       </c>
     </row>
@@ -2002,17 +2001,17 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>ODF形式</t>
+          <t>117段落 14表</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -2028,12 +2027,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -2054,17 +2053,17 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>ODF形式</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -2080,22 +2079,23 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町ヒアリング資料.docx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>3町へのヒアリング資料。設問はご確認を要する</t>
+          <t>会議で用いるヒアリングシート</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>138段落 11表</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>38段落 21表</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -2105,17 +2105,17 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町別の論点整理.xlsx</t>
+          <t>第10期計画_3町ヒアリング資料.docx</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点12件、3町共通の論点8件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
+          <t>3町へのヒアリング資料。設問はご確認を要する</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>138段落 11表</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
@@ -2130,44 +2130,69 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_3町別の論点整理.xlsx</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点12件、3町共通の論点8件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="34" customHeight="1">
+      <c r="A71" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B72" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="C72" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）29件／お諮りする内容を含む 29件</t>
-        </is>
-      </c>
-      <c r="D72" s="11" t="n"/>
-      <c r="E72" s="12" t="n"/>
-    </row>
-    <row r="74" ht="140" customHeight="1">
-      <c r="A74" s="13" t="inlineStr">
+      <c r="B73" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）29件／お諮りする内容を含む 30件</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="n"/>
+      <c r="E73" s="12" t="n"/>
+    </row>
+    <row r="75" ht="140" customHeight="1">
+      <c r="A75" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2178,16 +2203,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A64:E64"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="C73:E73"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A75:E75"/>
     <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>741段落 124表</t>
+          <t>750段落 124表</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1244,9 +1244,10 @@
           <t>8シート</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1256,23 +1257,22 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>8シート</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1282,22 +1282,23 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1307,17 +1308,17 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -1332,17 +1333,17 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -1357,17 +1358,17 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -1382,55 +1383,54 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>10シート</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>【5　基礎データの点検と突合】</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="34" customHeight="1">
-      <c r="A40" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>見える化B系列の受領点検</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>7シート</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>見える化D系列の受領点検</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>見える化D系列の受領点検</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -1492,17 +1492,17 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -1518,22 +1518,23 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1543,17 +1544,17 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -1568,23 +1569,22 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -1620,17 +1620,17 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -1698,22 +1698,23 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1723,55 +1724,55 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_基金条例の確認.xlsx</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>【6　ご確認・ご決定をお願いする資料】</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="34" customHeight="1">
-      <c r="A54" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1781,23 +1782,22 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1807,17 +1807,17 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -1833,17 +1833,17 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -1859,22 +1859,23 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1884,55 +1885,54 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>9シート</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>【7　工程】</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="34" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>187段落 8表</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1942,17 +1942,17 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>187段落 8表</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
@@ -1968,56 +1968,56 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_業務工程管理表.xlsx</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="34" customHeight="1">
+      <c r="A64" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>3シート</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>【8　会議】</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="34" customHeight="1">
-      <c r="A65" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>117段落 14表</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -2027,17 +2027,17 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>ODF形式</t>
+          <t>117段落 14表</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>ODF形式</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
@@ -2105,22 +2105,23 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町ヒアリング資料.docx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>3町へのヒアリング資料。設問はご確認を要する</t>
+          <t>会議で用いるヒアリングシート</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>138段落 11表</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>38段落 21表</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -2130,17 +2131,17 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町別の論点整理.xlsx</t>
+          <t>第10期計画_3町ヒアリング資料.docx</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点12件、3町共通の論点8件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
+          <t>3町へのヒアリング資料。設問はご確認を要する</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>138段落 11表</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -2155,44 +2156,69 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_3町別の論点整理.xlsx</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点12件、3町共通の論点8件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="34" customHeight="1">
+      <c r="A72" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="9" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B73" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）29件／お諮りする内容を含む 30件</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="n"/>
-      <c r="E73" s="12" t="n"/>
-    </row>
-    <row r="75" ht="140" customHeight="1">
-      <c r="A75" s="13" t="inlineStr">
+      <c r="B74" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）30件／お諮りする内容を含む 30件</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="n"/>
+      <c r="E74" s="12" t="n"/>
+    </row>
+    <row r="76" ht="140" customHeight="1">
+      <c r="A76" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2203,16 +2229,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A65:E65"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="C74:E74"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A61:E61"/>
     <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>750段落 124表</t>
+          <t>737段落 121表</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -2181,44 +2181,69 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>73段落 12表</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="34" customHeight="1">
+      <c r="A73" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="9" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B74" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）30件／お諮りする内容を含む 30件</t>
-        </is>
-      </c>
-      <c r="D74" s="11" t="n"/>
-      <c r="E74" s="12" t="n"/>
-    </row>
-    <row r="76" ht="140" customHeight="1">
-      <c r="A76" s="13" t="inlineStr">
+      <c r="B75" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）30件／お諮りする内容を含む 31件</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="n"/>
+      <c r="E75" s="12" t="n"/>
+    </row>
+    <row r="77" ht="140" customHeight="1">
+      <c r="A77" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2229,13 +2254,13 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A77:E77"/>
     <mergeCell ref="A65:E65"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A54:E54"/>
-    <mergeCell ref="C74:E74"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="C75:E75"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A61:E61"/>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2206,44 +2206,69 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>105段落 15表</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="34" customHeight="1">
+      <c r="A74" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="9" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B75" s="9" t="n">
-        <v>61</v>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）30件／お諮りする内容を含む 31件</t>
-        </is>
-      </c>
-      <c r="D75" s="11" t="n"/>
-      <c r="E75" s="12" t="n"/>
-    </row>
-    <row r="77" ht="140" customHeight="1">
-      <c r="A77" s="13" t="inlineStr">
+      <c r="B76" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）30件／お諮りする内容を含む 32件</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="n"/>
+      <c r="E76" s="12" t="n"/>
+    </row>
+    <row r="78" ht="140" customHeight="1">
+      <c r="A78" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2254,13 +2279,13 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A77:E77"/>
     <mergeCell ref="A65:E65"/>
+    <mergeCell ref="C76:E76"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A78:E78"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C75:E75"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A61:E61"/>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1043,35 +1043,36 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_9月作業_アンケート分析の作業状況.xlsx</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月工程のうちアンケート調査の集計・分析について作業状況を整理したもの。完了した作業、未了の作業と着手の条件、発注者のご判断を待っている事項4件、9月内の作業工程</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>10シート</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>【4　推計と分析】</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>9シート</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1081,17 +1082,17 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -1106,12 +1107,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1131,17 +1132,17 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>11シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -1156,17 +1157,17 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -1181,17 +1182,17 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
+          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -1206,17 +1207,17 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -1231,12 +1232,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1244,10 +1245,9 @@
           <t>8シート</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1270,9 +1270,10 @@
           <t>8シート</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1282,23 +1283,22 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>8シート</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1308,22 +1308,23 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1333,17 +1334,17 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -1358,17 +1359,17 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -1383,17 +1384,17 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
@@ -1408,55 +1409,54 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>10シート</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>【5　基礎データの点検と突合】</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="34" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>見える化B系列の受領点検</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>7シート</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>見える化D系列の受領点検</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -1492,17 +1492,17 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>見える化D系列の受領点検</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -1518,17 +1518,17 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -1544,22 +1544,23 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1569,17 +1570,17 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -1594,23 +1595,22 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1620,17 +1620,17 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
@@ -1646,17 +1646,17 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -1724,22 +1724,23 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1749,55 +1750,55 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_基金条例の確認.xlsx</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="A54" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>【6　ご確認・ご決定をお願いする資料】</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="34" customHeight="1">
-      <c r="A55" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1807,23 +1808,22 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -1859,17 +1859,17 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
@@ -1885,22 +1885,23 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1910,55 +1911,54 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="34" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>9シート</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>【7　工程】</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="34" customHeight="1">
-      <c r="A62" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>187段落 8表</t>
-        </is>
-      </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1968,17 +1968,17 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>187段落 8表</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -1994,56 +1994,56 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_業務工程管理表.xlsx</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="34" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>3シート</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>【8　会議】</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="34" customHeight="1">
-      <c r="A66" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>117段落 14表</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -2053,17 +2053,17 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>ODF形式</t>
+          <t>117段落 14表</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -2105,17 +2105,17 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>ODF形式</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -2131,22 +2131,23 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町ヒアリング資料.docx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>3町へのヒアリング資料。設問はご確認を要する</t>
+          <t>会議で用いるヒアリングシート</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>138段落 11表</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>38段落 21表</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -2156,17 +2157,17 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町別の論点整理.xlsx</t>
+          <t>第10期計画_3町ヒアリング資料.docx</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点12件、3町共通の論点8件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
+          <t>3町へのヒアリング資料。設問はご確認を要する</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>138段落 11表</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -2181,17 +2182,17 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_3町別の論点整理.xlsx</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点12件、3町共通の論点8件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>73段落 12表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
@@ -2206,17 +2207,17 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>105段落 15表</t>
+          <t>73段落 12表</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
@@ -2231,44 +2232,69 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>105段落 15表</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="34" customHeight="1">
+      <c r="A75" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="9" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B76" s="9" t="n">
-        <v>62</v>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）30件／お諮りする内容を含む 32件</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="n"/>
-      <c r="E76" s="12" t="n"/>
-    </row>
-    <row r="78" ht="140" customHeight="1">
-      <c r="A78" s="13" t="inlineStr">
+      <c r="B77" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）31件／お諮りする内容を含む 32件</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="n"/>
+      <c r="E77" s="12" t="n"/>
+    </row>
+    <row r="79" ht="140" customHeight="1">
+      <c r="A79" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2279,17 +2305,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A62:E62"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A78:E78"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="C77:E77"/>
     <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A79:E79"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -632,7 +632,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>［要協議］63件ほか90箇所の未確定事項を本文に残している。協議用であることを表紙に明示している</t>
+          <t>［要協議］ほか未確定事項を本文に残している。協議用であることを表紙に明示している</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1968,23 +1968,22 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>187段落 8表</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1994,17 +1993,17 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>187段落 8表</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -2020,56 +2019,56 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_業務工程管理表.xlsx</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="34" customHeight="1">
+      <c r="A66" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>3シート</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>【8　会議】</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="34" customHeight="1">
-      <c r="A67" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>117段落 14表</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2078,17 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>ODF形式</t>
+          <t>117段落 14表</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
@@ -2105,12 +2104,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -2131,17 +2130,17 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>ODF形式</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
@@ -2157,22 +2156,23 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町ヒアリング資料.docx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>3町へのヒアリング資料。設問はご確認を要する</t>
+          <t>会議で用いるヒアリングシート</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>138段落 11表</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>38段落 21表</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -2182,17 +2182,17 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町別の論点整理.xlsx</t>
+          <t>第10期計画_3町ヒアリング資料.docx</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点12件、3町共通の論点8件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
+          <t>3町へのヒアリング資料。設問はご確認を要する</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>138段落 11表</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
@@ -2207,17 +2207,17 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_3町別の論点整理.xlsx</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点19件、3町共通の論点9件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>73段落 12表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
@@ -2232,17 +2232,17 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>105段落 15表</t>
+          <t>73段落 12表</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
@@ -2257,44 +2257,69 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>105段落 15表</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="34" customHeight="1">
+      <c r="A76" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="9" t="inlineStr">
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B77" s="9" t="n">
-        <v>63</v>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）31件／お諮りする内容を含む 32件</t>
-        </is>
-      </c>
-      <c r="D77" s="11" t="n"/>
-      <c r="E77" s="12" t="n"/>
-    </row>
-    <row r="79" ht="140" customHeight="1">
-      <c r="A79" s="13" t="inlineStr">
+      <c r="B78" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）31件／お諮りする内容を含む 33件</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="n"/>
+      <c r="E78" s="12" t="n"/>
+    </row>
+    <row r="80" ht="140" customHeight="1">
+      <c r="A80" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2312,10 +2337,10 @@
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A41:E41"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A66:E66"/>
-    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="A80:E80"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A67:E67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -1600,12 +1600,12 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>6シート</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2232,17 +2232,17 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>73段落 12表</t>
+          <t>79段落 10表</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
@@ -2257,17 +2257,17 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>105段落 15表</t>
+          <t>73段落 12表</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
@@ -2282,44 +2282,69 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>105段落 15表</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="34" customHeight="1">
+      <c r="A77" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="9" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B78" s="9" t="n">
-        <v>64</v>
-      </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）31件／お諮りする内容を含む 33件</t>
-        </is>
-      </c>
-      <c r="D78" s="11" t="n"/>
-      <c r="E78" s="12" t="n"/>
-    </row>
-    <row r="80" ht="140" customHeight="1">
-      <c r="A80" s="13" t="inlineStr">
+      <c r="B79" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）31件／お諮りする内容を含む 34件</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="n"/>
+      <c r="E79" s="12" t="n"/>
+    </row>
+    <row r="81" ht="140" customHeight="1">
+      <c r="A81" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2332,13 +2357,13 @@
   <mergeCells count="11">
     <mergeCell ref="A55:E55"/>
     <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A81:E81"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A25:E25"/>
+    <mergeCell ref="C79:E79"/>
     <mergeCell ref="A41:E41"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="A80:E80"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A67:E67"/>
   </mergeCells>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1453,36 +1453,36 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_町別データシート.xlsx</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>【5　基礎データの点検と突合】</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>見える化B系列の受領点検</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>7シート</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>見える化D系列の受領点検</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -1518,17 +1518,17 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>見える化D系列の受領点検</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -1544,17 +1544,17 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -1570,22 +1570,23 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1595,17 +1596,17 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
@@ -1620,23 +1621,22 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1646,17 +1646,17 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -1750,22 +1750,23 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1775,55 +1776,55 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_基金条例の確認.xlsx</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="34" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>【6　ご確認・ご決定をお願いする資料】</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="34" customHeight="1">
-      <c r="A56" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1833,23 +1834,22 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1859,17 +1859,17 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
@@ -1885,17 +1885,17 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -1911,22 +1911,23 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1936,54 +1937,54 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="34" customHeight="1">
+      <c r="A62" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>9シート</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>【7　工程】</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="34" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>10シート</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1993,23 +1994,22 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>187段落 8表</t>
-        </is>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>10シート</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -2019,17 +2019,17 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>187段落 8表</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -2045,56 +2045,56 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_業務工程管理表.xlsx</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="34" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>3シート</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>【8　会議】</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="34" customHeight="1">
-      <c r="A68" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>117段落 14表</t>
-        </is>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -2104,17 +2104,17 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>ODF形式</t>
+          <t>117段落 14表</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -2156,17 +2156,17 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>ODF形式</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -2182,22 +2182,23 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町ヒアリング資料.docx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>3町へのヒアリング資料。設問はご確認を要する</t>
+          <t>会議で用いるヒアリングシート</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>138段落 11表</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>38段落 21表</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -2207,17 +2208,17 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町別の論点整理.xlsx</t>
+          <t>第10期計画_3町ヒアリング資料.docx</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点19件、3町共通の論点9件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
+          <t>3町へのヒアリング資料。設問はご確認を要する</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>138段落 11表</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
@@ -2232,17 +2233,17 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_3町別の論点整理.xlsx</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点19件、3町共通の論点9件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>79段落 10表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
@@ -2257,17 +2258,17 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>73段落 12表</t>
+          <t>79段落 10表</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
@@ -2282,17 +2283,17 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>105段落 15表</t>
+          <t>73段落 12表</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
@@ -2307,44 +2308,69 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>105段落 15表</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="34" customHeight="1">
+      <c r="A78" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="9" t="inlineStr">
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B79" s="9" t="n">
-        <v>65</v>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）31件／お諮りする内容を含む 34件</t>
-        </is>
-      </c>
-      <c r="D79" s="11" t="n"/>
-      <c r="E79" s="12" t="n"/>
-    </row>
-    <row r="81" ht="140" customHeight="1">
-      <c r="A81" s="13" t="inlineStr">
+      <c r="B80" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）32件／お諮りする内容を含む 34件</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="n"/>
+      <c r="E80" s="12" t="n"/>
+    </row>
+    <row r="82" ht="140" customHeight="1">
+      <c r="A82" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2355,17 +2381,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A81:E81"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A82:E82"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A56:E56"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -1464,7 +1464,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>737段落 121表</t>
+          <t>770段落 126表</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>105段落 15表</t>
+          <t>119段落 17表</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
@@ -2333,44 +2333,69 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="34" customHeight="1">
+      <c r="A79" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="9" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B80" s="9" t="n">
-        <v>66</v>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）32件／お諮りする内容を含む 34件</t>
-        </is>
-      </c>
-      <c r="D80" s="11" t="n"/>
-      <c r="E80" s="12" t="n"/>
-    </row>
-    <row r="82" ht="140" customHeight="1">
-      <c r="A82" s="13" t="inlineStr">
+      <c r="B81" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）32件／お諮りする内容を含む 35件</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="n"/>
+      <c r="E81" s="12" t="n"/>
+    </row>
+    <row r="83" ht="140" customHeight="1">
+      <c r="A83" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2381,17 +2406,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A83:E83"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A42:E42"/>
-    <mergeCell ref="C80:E80"/>
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A82:E82"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A56:E56"/>
+    <mergeCell ref="C81:E81"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>770段落 126表</t>
+          <t>783段落 127表</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2358,44 +2358,69 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="34" customHeight="1">
+      <c r="A80" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="9" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B81" s="9" t="n">
-        <v>67</v>
-      </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）32件／お諮りする内容を含む 35件</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="n"/>
-      <c r="E81" s="12" t="n"/>
-    </row>
-    <row r="83" ht="140" customHeight="1">
-      <c r="A83" s="13" t="inlineStr">
+      <c r="B82" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）32件／お諮りする内容を含む 36件</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="n"/>
+      <c r="E82" s="12" t="n"/>
+    </row>
+    <row r="84" ht="140" customHeight="1">
+      <c r="A84" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2406,7 +2431,6 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A83:E83"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A25:E25"/>
@@ -2414,9 +2438,10 @@
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A63:E63"/>
     <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="C82:E82"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A56:E56"/>
-    <mergeCell ref="C81:E81"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>783段落 127表</t>
+          <t>806段落 130表</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2383,44 +2383,69 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>10シート</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="34" customHeight="1">
+      <c r="A81" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="9" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B82" s="9" t="n">
-        <v>68</v>
-      </c>
-      <c r="C82" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）32件／お諮りする内容を含む 36件</t>
-        </is>
-      </c>
-      <c r="D82" s="11" t="n"/>
-      <c r="E82" s="12" t="n"/>
-    </row>
-    <row r="84" ht="140" customHeight="1">
-      <c r="A84" s="13" t="inlineStr">
+      <c r="B83" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）32件／お諮りする内容を含む 37件</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="n"/>
+      <c r="E83" s="12" t="n"/>
+    </row>
+    <row r="85" ht="140" customHeight="1">
+      <c r="A85" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2437,9 +2462,9 @@
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A85:E85"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A84:E84"/>
-    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="C83:E83"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A56:E56"/>
   </mergeCells>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2408,44 +2408,69 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定について、基準年度をどこに置くかを実測により整理し、給付費と保険料への影響を示したもの。数量の基準年度に使えるのは令和7年度だけであること、単価は令和8年度でも使えること、見える化システムの総括表（保険者単位）と計画作成支援ツール（3町合計）で水準が異なることを整理した。算定パターン8件のうち算定できた7件で、算定上の月額基準額は6,224円から7,049円まで825円の幅がある。採用パターン（令和7年度基準・総括表・認定者数シナリオ②）のご判断をお願いする事項2件と、確認をお願いする事項4件を含む</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>8シート</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="34" customHeight="1">
+      <c r="A82" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="9" t="inlineStr">
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B83" s="9" t="n">
-        <v>69</v>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）32件／お諮りする内容を含む 37件</t>
-        </is>
-      </c>
-      <c r="D83" s="11" t="n"/>
-      <c r="E83" s="12" t="n"/>
-    </row>
-    <row r="85" ht="140" customHeight="1">
-      <c r="A85" s="13" t="inlineStr">
+      <c r="B84" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）32件／お諮りする内容を含む 38件</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="n"/>
+      <c r="E84" s="12" t="n"/>
+    </row>
+    <row r="86" ht="140" customHeight="1">
+      <c r="A86" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2457,14 +2482,14 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A86:E86"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A42:E42"/>
+    <mergeCell ref="C84:E84"/>
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A85:E85"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="C83:E83"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A56:E56"/>
   </mergeCells>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2433,44 +2433,69 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="34" customHeight="1">
+      <c r="A83" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="9" t="inlineStr">
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B84" s="9" t="n">
-        <v>70</v>
-      </c>
-      <c r="C84" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）32件／お諮りする内容を含む 38件</t>
-        </is>
-      </c>
-      <c r="D84" s="11" t="n"/>
-      <c r="E84" s="12" t="n"/>
-    </row>
-    <row r="86" ht="140" customHeight="1">
-      <c r="A86" s="13" t="inlineStr">
+      <c r="B85" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）32件／お諮りする内容を含む 39件</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="n"/>
+      <c r="E85" s="12" t="n"/>
+    </row>
+    <row r="87" ht="140" customHeight="1">
+      <c r="A87" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2481,17 +2506,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A87:E87"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A86:E86"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A42:E42"/>
-    <mergeCell ref="C84:E84"/>
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A63:E63"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A56:E56"/>
+    <mergeCell ref="C85:E85"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2458,44 +2458,95 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="34" customHeight="1">
+      <c r="A84" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（10章・資料2）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、陥りやすい誤り。大雪地区広域連合の値は適用例として明示している。本業務の副産物であり、他団体への転用を想定している</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>153段落 13表</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="34" customHeight="1">
+      <c r="A85" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="9" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B85" s="9" t="n">
-        <v>71</v>
-      </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）32件／お諮りする内容を含む 39件</t>
-        </is>
-      </c>
-      <c r="D85" s="11" t="n"/>
-      <c r="E85" s="12" t="n"/>
-    </row>
-    <row r="87" ht="140" customHeight="1">
-      <c r="A87" s="13" t="inlineStr">
+      <c r="B87" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）33件／お諮りする内容を含む 40件</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="n"/>
+      <c r="E87" s="12" t="n"/>
+    </row>
+    <row r="89" ht="140" customHeight="1">
+      <c r="A89" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2506,17 +2557,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A87:E87"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A63:E63"/>
+    <mergeCell ref="C87:E87"/>
     <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A89:E89"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A56:E56"/>
-    <mergeCell ref="C85:E85"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2483,23 +2483,22 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（10章・資料2）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、陥りやすい誤り。大雪地区広域連合の値は適用例として明示している。本業務の副産物であり、他団体への転用を想定している</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>153段落 13表</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>10シート</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -2509,44 +2508,70 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
+          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（10章・資料2）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、陥りやすい誤り。大雪地区広域連合の値は適用例として明示している。本業務の副産物であり、他団体への転用を想定している</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>153段落 13表</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="34" customHeight="1">
+      <c r="A86" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="9" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B87" s="9" t="n">
-        <v>73</v>
-      </c>
-      <c r="C87" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）33件／お諮りする内容を含む 40件</t>
-        </is>
-      </c>
-      <c r="D87" s="11" t="n"/>
-      <c r="E87" s="12" t="n"/>
-    </row>
-    <row r="89" ht="140" customHeight="1">
-      <c r="A89" s="13" t="inlineStr">
+      <c r="B88" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）33件／お諮りする内容を含む 41件</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="n"/>
+      <c r="E88" s="12" t="n"/>
+    </row>
+    <row r="90" ht="140" customHeight="1">
+      <c r="A90" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2561,11 +2586,11 @@
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A90:E90"/>
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A63:E63"/>
-    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="C88:E88"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A89:E89"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A56:E56"/>
   </mergeCells>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2508,23 +2508,22 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（10章・資料2）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、陥りやすい誤り。大雪地区広域連合の値は適用例として明示している。本業務の副産物であり、他団体への転用を想定している</t>
+          <t>サービス見込量の算定に関する4件の成果品（基準年度とパターンの比較、季節性の検証と施策反映の設計、対計画比の偏りの補正試算、趨勢に現れない要因の分析）を1件に束ねた統合報告書。全36シートを収録したうえで、算定の全体像と採用案、月額への効きの統合一覧（24件）、記載事項の網羅点検（26事項。対応5・一部対応12・未対応9）、論点漏れの是正の方針（7件）、成果品の統合候補（7群）を新たに加えた。介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項と突き合わせ、中長期推計が認定者数にとどまること、地域支援事業の量の見込みがないことなどを論点漏れとして特定した。ご判断をお願いする事項6件を含む</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>153段落 13表</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>44シート</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -2534,44 +2533,70 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
+          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（10章・資料2）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、陥りやすい誤り。大雪地区広域連合の値は適用例として明示している。本業務の副産物であり、他団体への転用を想定している</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>197段落 18表</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="34" customHeight="1">
+      <c r="A87" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="9" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B88" s="9" t="n">
-        <v>74</v>
-      </c>
-      <c r="C88" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）33件／お諮りする内容を含む 41件</t>
-        </is>
-      </c>
-      <c r="D88" s="11" t="n"/>
-      <c r="E88" s="12" t="n"/>
-    </row>
-    <row r="90" ht="140" customHeight="1">
-      <c r="A90" s="13" t="inlineStr">
+      <c r="B89" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）33件／お諮りする内容を含む 42件</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="n"/>
+      <c r="E89" s="12" t="n"/>
+    </row>
+    <row r="91" ht="140" customHeight="1">
+      <c r="A91" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2582,14 +2607,14 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="C89:E89"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A90:E90"/>
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A63:E63"/>
-    <mergeCell ref="C88:E88"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A56:E56"/>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2533,23 +2533,22 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（10章・資料2）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、陥りやすい誤り。大雪地区広域連合の値は適用例として明示している。本業務の副産物であり、他団体への転用を想定している</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>197段落 18表</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -2559,44 +2558,70 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
+          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り。大雪地区広域連合の値は適用例として明示している。本業務の副産物であり、他団体への転用を想定している</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>197段落 18表</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="34" customHeight="1">
+      <c r="A88" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="9" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B89" s="9" t="n">
-        <v>75</v>
-      </c>
-      <c r="C89" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）33件／お諮りする内容を含む 42件</t>
-        </is>
-      </c>
-      <c r="D89" s="11" t="n"/>
-      <c r="E89" s="12" t="n"/>
-    </row>
-    <row r="91" ht="140" customHeight="1">
-      <c r="A91" s="13" t="inlineStr">
+      <c r="B90" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）33件／お諮りする内容を含む 43件</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="n"/>
+      <c r="E90" s="12" t="n"/>
+    </row>
+    <row r="92" ht="140" customHeight="1">
+      <c r="A92" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2607,8 +2632,6 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A91:E91"/>
-    <mergeCell ref="C89:E89"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A25:E25"/>
@@ -2616,8 +2639,10 @@
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A63:E63"/>
     <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C90:E90"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A92:E92"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2558,23 +2558,22 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り。大雪地区広域連合の値は適用例として明示している。本業務の副産物であり、他団体への転用を想定している</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。施設・居住系の画面から先へ進めない件の切り分けを7項目で示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>197段落 18表</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -2584,44 +2583,70 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
+          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り。大雪地区広域連合の値は適用例として明示している。本業務の副産物であり、他団体への転用を想定している</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>197段落 18表</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="34" customHeight="1">
+      <c r="A89" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="9" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B90" s="9" t="n">
-        <v>76</v>
-      </c>
-      <c r="C90" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）33件／お諮りする内容を含む 43件</t>
-        </is>
-      </c>
-      <c r="D90" s="11" t="n"/>
-      <c r="E90" s="12" t="n"/>
-    </row>
-    <row r="92" ht="140" customHeight="1">
-      <c r="A92" s="13" t="inlineStr">
+      <c r="B91" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）33件／お諮りする内容を含む 44件</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="n"/>
+      <c r="E91" s="12" t="n"/>
+    </row>
+    <row r="93" ht="140" customHeight="1">
+      <c r="A93" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2639,10 +2664,10 @@
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A63:E63"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="C91:E91"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A92:E92"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -2563,12 +2563,12 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。施設・居住系の画面から先へ進めない件の切り分けを7項目で示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項4件を含む</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2583,23 +2583,22 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り。大雪地区広域連合の値は適用例として明示している。本業務の副産物であり、他団体への転用を想定している</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の水準を置く案とした。施設・居住系7サービスは画面と同じ並びの実数を用意し（貼り付け用のシートを含む）、在宅22サービスは現在の計算値に乗じる倍率（令和7年度の利用率÷令和8年度の利用率）を用意した。施設・居住系は474人から482人へ8人増える向き、在宅は倍率が1を下回るものが多く減る向きである。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>197段落 18表</t>
-        </is>
-      </c>
-      <c r="E88" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>8シート</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -2609,44 +2608,70 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
+          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り。大雪地区広域連合の値は適用例として明示している。本業務の副産物であり、他団体への転用を想定している</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>197段落 18表</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="34" customHeight="1">
+      <c r="A90" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="9" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B91" s="9" t="n">
-        <v>77</v>
-      </c>
-      <c r="C91" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）33件／お諮りする内容を含む 44件</t>
-        </is>
-      </c>
-      <c r="D91" s="11" t="n"/>
-      <c r="E91" s="12" t="n"/>
-    </row>
-    <row r="93" ht="140" customHeight="1">
-      <c r="A93" s="13" t="inlineStr">
+      <c r="B92" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）33件／お諮りする内容を含む 45件</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="n"/>
+      <c r="E92" s="12" t="n"/>
+    </row>
+    <row r="94" ht="140" customHeight="1">
+      <c r="A94" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2664,8 +2689,8 @@
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A63:E63"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="C92:E92"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A56:E56"/>
   </mergeCells>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -2588,7 +2588,7 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の水準を置く案とした。施設・居住系7サービスは画面と同じ並びの実数を用意し（貼り付け用のシートを含む）、在宅22サービスは現在の計算値に乗じる倍率（令和7年度の利用率÷令和8年度の利用率）を用意した。施設・居住系は474人から482人へ8人増える向き、在宅は倍率が1を下回るものが多く減る向きである。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①は年報による確定値、②③は総括表詳細（１）の年間の延べ人月÷12、④は総括表詳細（３）の1人1月あたり利用回（日）数を乗じたもの。サービス計は確定値、要介護度別の内訳は按分による推定値である。画面の令和7年度の整数をそのまま貼らない理由を3点示し、小数版と整数版の両方を用意した。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -2588,7 +2588,7 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①は年報による確定値、②③は総括表詳細（１）の年間の延べ人月÷12、④は総括表詳細（３）の1人1月あたり利用回（日）数を乗じたもの。サービス計は確定値、要介護度別の内訳は按分による推定値である。画面の令和7年度の整数をそのまま貼らない理由を3点示し、小数版と整数版の両方を用意した。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、小数版と整数版の両方を用意した。ご確認をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -2588,7 +2588,7 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、小数版と整数版の両方を用意した。ご確認をお願いする事項2件を含む</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。ご判断・ご確認をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -2588,7 +2588,7 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。ご判断・ご確認をお願いする事項2件を含む</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -945,23 +945,22 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>実施済み調査の結果報告</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>10シート</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -971,17 +970,17 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>受領した調査データの点検記録</t>
+          <t>実施済み調査の結果報告</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -997,17 +996,17 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>受領した調査データの点検記録</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -1023,17 +1022,17 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -1049,17 +1048,17 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_9月作業_アンケート分析の作業状況.xlsx</t>
+          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月工程のうちアンケート調査の集計・分析について作業状況を整理したもの。完了した作業、未了の作業と着手の条件、発注者のご判断を待っている事項4件、9月内の作業工程</t>
+          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -1069,35 +1068,36 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_9月作業_アンケート分析の作業状況.xlsx</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月工程のうちアンケート調査の集計・分析について作業状況を整理したもの。完了した作業、未了の作業と着手の条件、発注者のご判断を待っている事項4件、9月内の作業工程</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>10シート</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>【4　推計と分析】</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>9シート</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1107,17 +1107,17 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>11シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
+          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1270,10 +1270,9 @@
           <t>8シート</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1282,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -1296,9 +1295,10 @@
           <t>8シート</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1308,23 +1308,22 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>8シート</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1334,22 +1333,23 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1359,17 +1359,17 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -1384,17 +1384,17 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
@@ -1409,17 +1409,17 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -1434,17 +1434,17 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>所得段階の設定に関する検討。試算を含む</t>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -1459,56 +1459,55 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>所得段階の設定に関する検討。試算を含む</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>10シート</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>送付可能
 （留保明記済み）</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>【5　基礎データの点検と突合】</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>見える化B系列の受領点検</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>7シート</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1517,12 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>見える化D系列の受領点検</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -1544,17 +1543,17 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>見える化D系列の受領点検</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -1570,17 +1569,17 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -1596,22 +1595,23 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1621,17 +1621,17 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
@@ -1646,23 +1646,22 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1672,17 +1671,17 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -1698,17 +1697,17 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -1724,12 +1723,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -1750,12 +1749,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -1776,22 +1775,23 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1801,55 +1801,55 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_基金条例の確認.xlsx</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="34" customHeight="1">
+      <c r="A56" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>送付可能
 （留保明記済み）</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>【6　ご確認・ご決定をお願いする資料】</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="34" customHeight="1">
-      <c r="A57" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1859,23 +1859,22 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1885,17 +1884,17 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -1911,17 +1910,17 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
@@ -1937,22 +1936,23 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1962,54 +1962,54 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>9シート</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>【7　工程】</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="34" customHeight="1">
-      <c r="A64" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>10シート</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -2019,23 +2019,22 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>187段落 8表</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>10シート</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -2045,17 +2044,17 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>187段落 8表</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
@@ -2071,17 +2070,17 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -2091,36 +2090,36 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>【8　会議】</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="34" customHeight="1">
-      <c r="A69" s="5" t="n">
+    <row r="68" ht="34" customHeight="1">
+      <c r="A68" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>117段落 14表</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_送付資料一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>送付可能
 （留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>【8　会議】</t>
         </is>
       </c>
     </row>
@@ -2130,17 +2129,17 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>ODF形式</t>
+          <t>117段落 14表</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
@@ -2156,12 +2155,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -2182,17 +2181,17 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>ODF形式</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
@@ -2208,22 +2207,23 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町ヒアリング資料.docx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>3町へのヒアリング資料。設問はご確認を要する</t>
+          <t>会議で用いるヒアリングシート</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>138段落 11表</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>38段落 21表</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -2233,17 +2233,17 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町別の論点整理.xlsx</t>
+          <t>第10期計画_3町ヒアリング資料.docx</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点19件、3町共通の論点9件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
+          <t>3町へのヒアリング資料。設問はご確認を要する</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>138段落 11表</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
@@ -2258,17 +2258,17 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_3町別の論点整理.xlsx</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点19件、3町共通の論点9件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>79段落 10表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>73段落 12表</t>
+          <t>79段落 10表</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
@@ -2308,17 +2308,17 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>119段落 17表</t>
+          <t>73段落 12表</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
@@ -2333,17 +2333,17 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>119段落 17表</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
@@ -2408,17 +2408,17 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定について、基準年度をどこに置くかを実測により整理し、給付費と保険料への影響を示したもの。数量の基準年度に使えるのは令和7年度だけであること、単価は令和8年度でも使えること、見える化システムの総括表（保険者単位）と計画作成支援ツール（3町合計）で水準が異なることを整理した。算定パターン8件のうち算定できた7件で、算定上の月額基準額は6,224円から7,049円まで825円の幅がある。採用パターン（令和7年度基準・総括表・認定者数シナリオ②）のご判断をお願いする事項2件と、確認をお願いする事項4件を含む</t>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -2433,17 +2433,17 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>サービス見込量の算定について、基準年度をどこに置くかを実測により整理し、給付費と保険料への影響を示したもの。数量の基準年度に使えるのは令和7年度だけであること、単価は令和8年度でも使えること、見える化システムの総括表（保険者単位）と計画作成支援ツール（3町合計）で水準が異なることを整理した。算定パターン8件のうち算定できた7件で、算定上の月額基準額は6,224円から7,049円まで825円の幅がある。採用パターン（令和7年度基準・総括表・認定者数シナリオ②）のご判断をお願いする事項2件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -2483,17 +2483,17 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -2508,17 +2508,17 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に関する4件の成果品（基準年度とパターンの比較、季節性の検証と施策反映の設計、対計画比の偏りの補正試算、趨勢に現れない要因の分析）を1件に束ねた統合報告書。全36シートを収録したうえで、算定の全体像と採用案、月額への効きの統合一覧（24件）、記載事項の網羅点検（26事項。対応5・一部対応12・未対応9）、論点漏れの是正の方針（7件）、成果品の統合候補（7群）を新たに加えた。介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項と突き合わせ、中長期推計が認定者数にとどまること、地域支援事業の量の見込みがないことなどを論点漏れとして特定した。ご判断をお願いする事項6件を含む</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>44シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -2533,17 +2533,17 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
+          <t>サービス見込量の算定に関する4件の成果品（基準年度とパターンの比較、季節性の検証と施策反映の設計、対計画比の偏りの補正試算、趨勢に現れない要因の分析）を1件に束ねた統合報告書。全36シートを収録したうえで、算定の全体像と採用案、月額への効きの統合一覧（24件）、記載事項の網羅点検（26事項。対応5・一部対応12・未対応9）、論点漏れの是正の方針（7件）、成果品の統合候補（7群）を新たに加えた。介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項と突き合わせ、中長期推計が認定者数にとどまること、地域支援事業の量の見込みがないことなどを論点漏れとして特定した。ご判断をお願いする事項6件を含む</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>44シート</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -2583,17 +2583,17 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
@@ -2608,23 +2608,22 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り。大雪地区広域連合の値は適用例として明示している。本業務の副産物であり、他団体への転用を想定している</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>197段落 18表</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>8シート</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -2634,44 +2633,70 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
+          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り。大雪地区広域連合の値は適用例として明示している。本業務の副産物であり、他団体への転用を想定している</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>197段落 18表</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="34" customHeight="1">
+      <c r="A91" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="9" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B92" s="9" t="n">
-        <v>78</v>
-      </c>
-      <c r="C92" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）33件／お諮りする内容を含む 45件</t>
-        </is>
-      </c>
-      <c r="D92" s="11" t="n"/>
-      <c r="E92" s="12" t="n"/>
-    </row>
-    <row r="94" ht="140" customHeight="1">
-      <c r="A94" s="13" t="inlineStr">
+      <c r="B93" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）33件／お諮りする内容を含む 46件</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="n"/>
+      <c r="E93" s="12" t="n"/>
+    </row>
+    <row r="95" ht="140" customHeight="1">
+      <c r="A95" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2682,17 +2707,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A64:E64"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="A95:E95"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A94:E94"/>
-    <mergeCell ref="C92:E92"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A56:E56"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_送付資料一覧.xlsx
+++ b/output/第10期計画_送付資料一覧.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -722,35 +722,35 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>【2　第9期計画の評価・検証（令和8年8月の提出物）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>112段落 16表</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -760,23 +760,22 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告の根拠対照表.xlsx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>中間報告の記述と出典の対照。第三者検証用の索引</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>112段落 16表</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -786,22 +785,23 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_中間報告の根拠対照表.xlsx</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
+          <t>中間報告の記述と出典の対照。第三者検証用の索引</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>24シート</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -811,17 +811,17 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>24シート</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -836,12 +836,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -861,55 +861,54 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>5シート</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>【3　調査の集計と分析】</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>4調査の集計。限界と留保を各シートに明記している</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>15シート</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -919,17 +918,17 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>4調査の集計。限界と留保を各シートに明記している</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>24シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -945,22 +944,23 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>10シート</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>24シート</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -970,23 +970,22 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>実施済み調査の結果報告</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>475段落 51表</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>10シート</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -996,17 +995,17 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>受領した調査データの点検記録</t>
+          <t>実施済み調査の結果報告</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>16シート</t>
+          <t>475段落 51表</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -1022,17 +1021,17 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>受領した調査データの点検記録</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>16シート</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -1048,17 +1047,17 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -1074,17 +1073,17 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_9月作業_アンケート分析の作業状況.xlsx</t>
+          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月工程のうちアンケート調査の集計・分析について作業状況を整理したもの。完了した作業、未了の作業と着手の条件、発注者のご判断を待っている事項4件、9月内の作業工程</t>
+          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -1094,35 +1093,36 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_9月作業_アンケート分析の作業状況.xlsx</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月工程のうちアンケート調査の集計・分析について作業状況を整理したもの。完了した作業、未了の作業と着手の条件、発注者のご判断を待っている事項4件、9月内の作業工程</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>10シート</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>【4　推計と分析】</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>9シート</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1132,17 +1132,17 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>11シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>11シート</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
+          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -1295,10 +1295,9 @@
           <t>8シート</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1307,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -1321,9 +1320,10 @@
           <t>8シート</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1333,23 +1333,22 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>8シート</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1359,22 +1358,23 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1384,17 +1384,17 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
@@ -1409,17 +1409,17 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>15シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -1434,17 +1434,17 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>15シート</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -1459,17 +1459,17 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>所得段階の設定に関する検討。試算を含む</t>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -1484,56 +1484,55 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>所得段階の設定に関する検討。試算を含む</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>10シート</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>送付可能
 （留保明記済み）</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>【5　基礎データの点検と突合】</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="34" customHeight="1">
-      <c r="A44" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>見える化B系列の受領点検</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>7シート</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1542,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>見える化D系列の受領点検</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -1569,17 +1568,17 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>見える化D系列の受領点検</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>12シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -1595,17 +1594,17 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>12シート</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -1621,22 +1620,23 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>7シート</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1646,17 +1646,17 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
@@ -1671,23 +1671,22 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>4シート</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1697,17 +1696,17 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>4シート</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -1723,17 +1722,17 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>5シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
@@ -1749,12 +1748,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -1775,12 +1774,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -1801,22 +1800,23 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>5シート</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1826,55 +1826,55 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_基金条例の確認.xlsx</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="34" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>7シート</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>送付可能
 （留保明記済み）</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>【6　ご確認・ご決定をお願いする資料】</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="34" customHeight="1">
-      <c r="A58" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>3シート</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1884,23 +1884,22 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -1910,17 +1909,17 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>102段落 19表</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
@@ -1936,17 +1935,17 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>102段落 19表</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -1962,22 +1961,23 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>6シート</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>9シート</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -1987,54 +1987,54 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>6シート</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="34" customHeight="1">
+      <c r="A64" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>9シート</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>【7　工程】</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="34" customHeight="1">
-      <c r="A65" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>10シート</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -2044,23 +2044,22 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>187段落 8表</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>10シート</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -2070,17 +2069,17 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>187段落 8表</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -2096,17 +2095,17 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>3シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
@@ -2116,36 +2115,36 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>【8　会議】</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="34" customHeight="1">
-      <c r="A70" s="5" t="n">
+    <row r="69" ht="34" customHeight="1">
+      <c r="A69" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>117段落 14表</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画_送付資料一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>3シート</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
         <is>
           <t>送付可能
 （留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>【8　会議】</t>
         </is>
       </c>
     </row>
@@ -2155,17 +2154,17 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>ODF形式</t>
+          <t>117段落 14表</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -2181,12 +2180,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -2207,17 +2206,17 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>38段落 21表</t>
+          <t>ODF形式</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -2233,22 +2232,23 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町ヒアリング資料.docx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>3町へのヒアリング資料。設問はご確認を要する</t>
+          <t>会議で用いるヒアリングシート</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>138段落 11表</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
+          <t>38段落 21表</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
         </is>
       </c>
     </row>
@@ -2258,17 +2258,17 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_3町別の論点整理.xlsx</t>
+          <t>第10期計画_3町ヒアリング資料.docx</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点19件、3町共通の論点9件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
+          <t>3町へのヒアリング資料。設問はご確認を要する</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>138段落 11表</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_3町別の論点整理.xlsx</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点19件、3町共通の論点9件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>79段落 10表</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
@@ -2308,17 +2308,17 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>73段落 12表</t>
+          <t>79段落 10表</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
@@ -2333,17 +2333,17 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>119段落 17表</t>
+          <t>73段落 12表</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>119段落 17表</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>7シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
@@ -2408,17 +2408,17 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>7シート</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -2433,17 +2433,17 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定について、基準年度をどこに置くかを実測により整理し、給付費と保険料への影響を示したもの。数量の基準年度に使えるのは令和7年度だけであること、単価は令和8年度でも使えること、見える化システムの総括表（保険者単位）と計画作成支援ツール（3町合計）で水準が異なることを整理した。算定パターン8件のうち算定できた7件で、算定上の月額基準額は6,224円から7,049円まで825円の幅がある。採用パターン（令和7年度基準・総括表・認定者数シナリオ②）のご判断をお願いする事項2件と、確認をお願いする事項4件を含む</t>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
@@ -2458,17 +2458,17 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>サービス見込量の算定について、基準年度をどこに置くかを実測により整理し、給付費と保険料への影響を示したもの。数量の基準年度に使えるのは令和7年度だけであること、単価は令和8年度でも使えること、見える化システムの総括表（保険者単位）と計画作成支援ツール（3町合計）で水準が異なることを整理した。算定パターン8件のうち算定できた7件で、算定上の月額基準額は6,224円から7,049円まで825円の幅がある。採用パターン（令和7年度基準・総括表・認定者数シナリオ②）のご判断をお願いする事項2件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>8シート</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -2508,17 +2508,17 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>10シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -2533,17 +2533,17 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に関する4件の成果品（基準年度とパターンの比較、季節性の検証と施策反映の設計、対計画比の偏りの補正試算、趨勢に現れない要因の分析）を1件に束ねた統合報告書。全36シートを収録したうえで、算定の全体像と採用案、月額への効きの統合一覧（24件）、記載事項の網羅点検（26事項。対応5・一部対応12・未対応9）、論点漏れの是正の方針（7件）、成果品の統合候補（7群）を新たに加えた。介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項と突き合わせ、中長期推計が認定者数にとどまること、地域支援事業の量の見込みがないことなどを論点漏れとして特定した。ご判断をお願いする事項6件を含む</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>44シート</t>
+          <t>10シート</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
@@ -2558,17 +2558,17 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
+          <t>サービス見込量の算定に関する4件の成果品（基準年度とパターンの比較、季節性の検証と施策反映の設計、対計画比の偏りの補正試算、趨勢に現れない要因の分析）を1件に束ねた統合報告書。全36シートを収録したうえで、算定の全体像と採用案、月額への効きの統合一覧（24件）、記載事項の網羅点検（26事項。対応5・一部対応12・未対応9）、論点漏れの是正の方針（7件）、成果品の統合候補（7群）を新たに加えた。介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項と突き合わせ、中長期推計が認定者数にとどまること、地域支援事業の量の見込みがないことなどを論点漏れとして特定した。ご判断をお願いする事項6件を含む</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>9シート</t>
+          <t>44シート</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -2608,17 +2608,17 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>8シート</t>
+          <t>9シート</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
@@ -2633,23 +2633,22 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り。大雪地区広域連合の値は適用例として明示している。本業務の副産物であり、他団体への転用を想定している</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>197段落 18表</t>
-        </is>
-      </c>
-      <c r="E90" s="8" t="inlineStr">
-        <is>
-          <t>送付可能
-（留保明記済み）</t>
+          <t>8シート</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
         </is>
       </c>
     </row>
@@ -2659,44 +2658,70 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
+          <t>介護保険事業計画_サービス見込量算定の手引き.docx</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定方法を他の保険者でも用いられる形に一般化した手引き（12章・資料2）。基準年度の決め方、出所の選び方、算定パターンの列挙と比較、伸びの置き方、季節性の扱い、施策反映の設計と歯止め、供給実現性と需給差、自己点検の設計、趨勢に現れない要因と報酬改定、記載事項の網羅点検、陥りやすい誤り。大雪地区広域連合の値は適用例として明示している。本業務の副産物であり、他団体への転用を想定している</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>197段落 18表</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>送付可能
+（留保明記済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="34" customHeight="1">
+      <c r="A92" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
           <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
         <is>
           <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>80段落 27表</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="9" t="inlineStr">
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B93" s="9" t="n">
-        <v>79</v>
-      </c>
-      <c r="C93" s="10" t="inlineStr">
-        <is>
-          <t>うち 送付可能（留保明記済み）33件／お諮りする内容を含む 46件</t>
-        </is>
-      </c>
-      <c r="D93" s="11" t="n"/>
-      <c r="E93" s="12" t="n"/>
-    </row>
-    <row r="95" ht="140" customHeight="1">
-      <c r="A95" s="13" t="inlineStr">
+      <c r="B94" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>うち 送付可能（留保明記済み）33件／お諮りする内容を含む 47件</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="n"/>
+      <c r="E94" s="12" t="n"/>
+    </row>
+    <row r="96" ht="140" customHeight="1">
+      <c r="A96" s="13" t="inlineStr">
         <is>
           <t>注1）「お諮りする内容を含む」の資料は、受託者が現時点で受領している資料の範囲で作成した案・試算・判定を含みます。ご決定は発注者及び策定委員会において行っていただくものです。
 注2）計画素案は「協議用素案（令和8年8月時点）」です。本文には［要協議］［要確認］［要内訳］を残しています。所在と決定の単位は「発注者確認事項一覧」をご覧ください。
@@ -2707,17 +2732,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A96:E96"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C93:E93"/>
-    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
